--- a/temp/diversos/Bobinagem.xlsx
+++ b/temp/diversos/Bobinagem.xlsx
@@ -11,20 +11,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="46">
+  <si>
+    <t>EIXO AGL P39 P/ VENTOINHA</t>
+  </si>
+  <si>
+    <t>UNIDADE</t>
+  </si>
+  <si>
+    <t>UN</t>
+  </si>
+  <si>
+    <t/>
+  </si>
   <si>
     <t>ESTATOR BOBINADO AGL BV/NEW BV/PIVO P28 1/5 cv 04 42 220V 50Hz</t>
   </si>
   <si>
-    <t>UNIDADE</t>
-  </si>
-  <si>
-    <t>UN</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>ESTATOR BOBINADO AGL BV/NEW BV/PIVO P33 1/3 cv 04 42z 220V 50Hz</t>
   </si>
   <si>
@@ -127,9 +130,6 @@
     <t>ESTATOR P28 DESLIZANTE WEG 220V 60HZ</t>
   </si>
   <si>
-    <t>ESTATOR P35 DESLIZANTE WEG 127V 60HZ</t>
-  </si>
-  <si>
     <t>ESTATOR P35 DESLIZANTE WEG 220V 60HZ</t>
   </si>
   <si>
@@ -137,12 +137,6 @@
   </si>
   <si>
     <t>ROTOR AGL DESL P24 4 POLOS EIXO C/ VENTOINHA</t>
-  </si>
-  <si>
-    <t>ROTOR AGL DESL P28 2 POLOS EIXO C/ VENTOINHA</t>
-  </si>
-  <si>
-    <t>ROTOR AGL DESL P39 4 POLOS EIXO C/ VENTOINHA</t>
   </si>
   <si>
     <t>ROTOR AGL NEW BV P28 4 POLOS</t>
@@ -256,7 +250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" width="7.33203125" min="1" max="1"/>
@@ -272,7 +266,7 @@
   <sheetData>
     <row r="1" customHeight="1" ht="15" spans="1:10">
       <c r="A1" s="1" t="n">
-        <v>412145</v>
+        <v>813346</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -287,7 +281,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>40</v>
+        <v>464</v>
       </c>
       <c r="G1" s="3" t="n">
         <v>0</v>
@@ -304,7 +298,7 @@
     </row>
     <row r="2" customHeight="1" ht="15" spans="1:10">
       <c r="A2" s="1" t="n">
-        <v>412149</v>
+        <v>412145</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>4</v>
@@ -319,7 +313,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -336,7 +330,7 @@
     </row>
     <row r="3" customHeight="1" ht="15" spans="1:10">
       <c r="A3" s="1" t="n">
-        <v>412032</v>
+        <v>412149</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -351,7 +345,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -368,7 +362,7 @@
     </row>
     <row r="4" customHeight="1" ht="15" spans="1:10">
       <c r="A4" s="1" t="n">
-        <v>412031</v>
+        <v>412032</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
@@ -383,7 +377,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -400,7 +394,7 @@
     </row>
     <row r="5" customHeight="1" ht="15" spans="1:10">
       <c r="A5" s="1" t="n">
-        <v>412156</v>
+        <v>412031</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
@@ -415,7 +409,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1823</v>
+        <v>70</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -432,7 +426,7 @@
     </row>
     <row r="6" customHeight="1" ht="15" spans="1:10">
       <c r="A6" s="1" t="n">
-        <v>412080</v>
+        <v>412156</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>8</v>
@@ -447,7 +441,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>586</v>
+        <v>2229</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -464,7 +458,7 @@
     </row>
     <row r="7" customHeight="1" ht="15" spans="1:10">
       <c r="A7" s="1" t="n">
-        <v>412152</v>
+        <v>412080</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>9</v>
@@ -479,7 +473,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>68</v>
+        <v>586</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -496,7 +490,7 @@
     </row>
     <row r="8" customHeight="1" ht="15" spans="1:10">
       <c r="A8" s="1" t="n">
-        <v>412160</v>
+        <v>412152</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>10</v>
@@ -511,7 +505,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>274</v>
+        <v>68</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -528,7 +522,7 @@
     </row>
     <row r="9" customHeight="1" ht="15" spans="1:10">
       <c r="A9" s="1" t="n">
-        <v>412065</v>
+        <v>412160</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>11</v>
@@ -543,7 +537,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>585</v>
+        <v>274</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -560,7 +554,7 @@
     </row>
     <row r="10" customHeight="1" ht="15" spans="1:10">
       <c r="A10" s="1" t="n">
-        <v>412006</v>
+        <v>412065</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>12</v>
@@ -575,7 +569,7 @@
         <v>3</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>64</v>
+        <v>585</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
@@ -592,7 +586,7 @@
     </row>
     <row r="11" customHeight="1" ht="15" spans="1:10">
       <c r="A11" s="1" t="n">
-        <v>412146</v>
+        <v>412006</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>13</v>
@@ -607,7 +601,7 @@
         <v>3</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0</v>
@@ -624,7 +618,7 @@
     </row>
     <row r="12" customHeight="1" ht="15" spans="1:10">
       <c r="A12" s="1" t="n">
-        <v>412026</v>
+        <v>412146</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>14</v>
@@ -639,7 +633,7 @@
         <v>3</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -656,7 +650,7 @@
     </row>
     <row r="13" customHeight="1" ht="15" spans="1:10">
       <c r="A13" s="1" t="n">
-        <v>412148</v>
+        <v>412026</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>15</v>
@@ -671,7 +665,7 @@
         <v>3</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>447</v>
+        <v>56</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0</v>
@@ -688,7 +682,7 @@
     </row>
     <row r="14" customHeight="1" ht="15" spans="1:10">
       <c r="A14" s="1" t="n">
-        <v>412154</v>
+        <v>412148</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>16</v>
@@ -703,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>109</v>
+        <v>447</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0</v>
@@ -720,7 +714,7 @@
     </row>
     <row r="15" customHeight="1" ht="15" spans="1:10">
       <c r="A15" s="1" t="n">
-        <v>412101</v>
+        <v>412154</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>17</v>
@@ -735,7 +729,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
@@ -752,7 +746,7 @@
     </row>
     <row r="16" customHeight="1" ht="15" spans="1:10">
       <c r="A16" s="1" t="n">
-        <v>412164</v>
+        <v>412101</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>18</v>
@@ -767,7 +761,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>472</v>
+        <v>27</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>0</v>
@@ -784,7 +778,7 @@
     </row>
     <row r="17" customHeight="1" ht="15" spans="1:10">
       <c r="A17" s="1" t="n">
-        <v>412064</v>
+        <v>412164</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>19</v>
@@ -799,7 +793,7 @@
         <v>3</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>799</v>
+        <v>472</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0</v>
@@ -816,7 +810,7 @@
     </row>
     <row r="18" customHeight="1" ht="15" spans="1:10">
       <c r="A18" s="1" t="n">
-        <v>412157</v>
+        <v>412064</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>20</v>
@@ -831,7 +825,7 @@
         <v>3</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>177</v>
+        <v>799</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>0</v>
@@ -848,7 +842,7 @@
     </row>
     <row r="19" customHeight="1" ht="15" spans="1:10">
       <c r="A19" s="1" t="n">
-        <v>412159</v>
+        <v>412157</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>21</v>
@@ -863,7 +857,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>0</v>
@@ -880,7 +874,7 @@
     </row>
     <row r="20" customHeight="1" ht="15" spans="1:10">
       <c r="A20" s="1" t="n">
-        <v>412187</v>
+        <v>412159</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>22</v>
@@ -895,7 +889,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>31</v>
+        <v>125</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>0</v>
@@ -912,7 +906,7 @@
     </row>
     <row r="21" customHeight="1" ht="15" spans="1:10">
       <c r="A21" s="1" t="n">
-        <v>412102</v>
+        <v>412187</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>23</v>
@@ -927,7 +921,7 @@
         <v>3</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
@@ -944,7 +938,7 @@
     </row>
     <row r="22" customHeight="1" ht="15" spans="1:10">
       <c r="A22" s="1" t="n">
-        <v>412040</v>
+        <v>412102</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>24</v>
@@ -959,7 +953,7 @@
         <v>3</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>228</v>
+        <v>99</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>0</v>
@@ -976,7 +970,7 @@
     </row>
     <row r="23" customHeight="1" ht="15" spans="1:10">
       <c r="A23" s="1" t="n">
-        <v>412167</v>
+        <v>412040</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>25</v>
@@ -991,7 +985,7 @@
         <v>3</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0</v>
@@ -1008,7 +1002,7 @@
     </row>
     <row r="24" customHeight="1" ht="15" spans="1:10">
       <c r="A24" s="1" t="n">
-        <v>412376</v>
+        <v>412167</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>26</v>
@@ -1023,7 +1017,7 @@
         <v>3</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>3</v>
+        <v>191</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>0</v>
@@ -1040,7 +1034,7 @@
     </row>
     <row r="25" customHeight="1" ht="15" spans="1:10">
       <c r="A25" s="1" t="n">
-        <v>412014</v>
+        <v>412376</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>27</v>
@@ -1055,7 +1049,7 @@
         <v>3</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0</v>
@@ -1072,7 +1066,7 @@
     </row>
     <row r="26" customHeight="1" ht="15" spans="1:10">
       <c r="A26" s="1" t="n">
-        <v>412169</v>
+        <v>412014</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>28</v>
@@ -1087,7 +1081,7 @@
         <v>3</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>0</v>
@@ -1104,7 +1098,7 @@
     </row>
     <row r="27" customHeight="1" ht="15" spans="1:10">
       <c r="A27" s="1" t="n">
-        <v>412158</v>
+        <v>412169</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>29</v>
@@ -1119,7 +1113,7 @@
         <v>3</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>0</v>
@@ -1136,7 +1130,7 @@
     </row>
     <row r="28" customHeight="1" ht="15" spans="1:10">
       <c r="A28" s="1" t="n">
-        <v>412121</v>
+        <v>412158</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>30</v>
@@ -1151,7 +1145,7 @@
         <v>3</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>454</v>
+        <v>52</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0</v>
@@ -1168,7 +1162,7 @@
     </row>
     <row r="29" customHeight="1" ht="15" spans="1:10">
       <c r="A29" s="1" t="n">
-        <v>412120</v>
+        <v>412121</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>31</v>
@@ -1183,7 +1177,7 @@
         <v>3</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>42</v>
+        <v>454</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0</v>
@@ -1200,7 +1194,7 @@
     </row>
     <row r="30" customHeight="1" ht="15" spans="1:10">
       <c r="A30" s="1" t="n">
-        <v>412024</v>
+        <v>412120</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>32</v>
@@ -1215,7 +1209,7 @@
         <v>3</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1651</v>
+        <v>42</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>0</v>
@@ -1232,7 +1226,7 @@
     </row>
     <row r="31" customHeight="1" ht="15" spans="1:10">
       <c r="A31" s="1" t="n">
-        <v>412151</v>
+        <v>412024</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>33</v>
@@ -1247,7 +1241,7 @@
         <v>3</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>927</v>
+        <v>1651</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0</v>
@@ -1264,7 +1258,7 @@
     </row>
     <row r="32" customHeight="1" ht="15" spans="1:10">
       <c r="A32" s="1" t="n">
-        <v>412038</v>
+        <v>412151</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>34</v>
@@ -1279,7 +1273,7 @@
         <v>3</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>295</v>
+        <v>927</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>0</v>
@@ -1296,7 +1290,7 @@
     </row>
     <row r="33" customHeight="1" ht="15" spans="1:10">
       <c r="A33" s="1" t="n">
-        <v>412374</v>
+        <v>412038</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>35</v>
@@ -1311,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>377</v>
+        <v>295</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0</v>
@@ -1328,7 +1322,7 @@
     </row>
     <row r="34" customHeight="1" ht="15" spans="1:10">
       <c r="A34" s="1" t="n">
-        <v>412396</v>
+        <v>412374</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>36</v>
@@ -1343,7 +1337,7 @@
         <v>3</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>191</v>
+        <v>377</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0</v>
@@ -1360,7 +1354,7 @@
     </row>
     <row r="35" customHeight="1" ht="15" spans="1:10">
       <c r="A35" s="1" t="n">
-        <v>412395</v>
+        <v>412396</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>37</v>
@@ -1375,7 +1369,7 @@
         <v>3</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>6</v>
+        <v>191</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0</v>
@@ -1392,7 +1386,7 @@
     </row>
     <row r="36" customHeight="1" ht="15" spans="1:10">
       <c r="A36" s="1" t="n">
-        <v>412375</v>
+        <v>412395</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>38</v>
@@ -1407,7 +1401,7 @@
         <v>3</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1142</v>
+        <v>6</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0</v>
@@ -1520,7 +1514,7 @@
     </row>
     <row r="40" customHeight="1" ht="15" spans="1:10">
       <c r="A40" s="1" t="n">
-        <v>412062</v>
+        <v>412147</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>42</v>
@@ -1535,7 +1529,7 @@
         <v>3</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>355</v>
+        <v>2813</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0</v>
@@ -1552,7 +1546,7 @@
     </row>
     <row r="41" customHeight="1" ht="15" spans="1:10">
       <c r="A41" s="1" t="n">
-        <v>412112</v>
+        <v>412162</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>43</v>
@@ -1567,7 +1561,7 @@
         <v>3</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>205</v>
+        <v>511</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>0</v>
@@ -1584,7 +1578,7 @@
     </row>
     <row r="42" customHeight="1" ht="15" spans="1:10">
       <c r="A42" s="1" t="n">
-        <v>412147</v>
+        <v>412163</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>44</v>
@@ -1599,7 +1593,7 @@
         <v>3</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2813</v>
+        <v>466</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>0</v>
@@ -1616,7 +1610,7 @@
     </row>
     <row r="43" customHeight="1" ht="15" spans="1:10">
       <c r="A43" s="1" t="n">
-        <v>412162</v>
+        <v>412393</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>45</v>
@@ -1631,7 +1625,7 @@
         <v>3</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>511</v>
+        <v>619</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>0</v>
@@ -1643,70 +1637,6 @@
         <v>0</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" ht="15" spans="1:10">
-      <c r="A44" s="1" t="n">
-        <v>412163</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>466</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" ht="15" spans="1:10">
-      <c r="A45" s="1" t="n">
-        <v>412393</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>619</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/temp/diversos/Bobinagem.xlsx
+++ b/temp/diversos/Bobinagem.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="47">
   <si>
     <t>EIXO AGL P39 P/ VENTOINHA</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>ESTATOR P47 DESLIZANTE WEG 127V 60HZ</t>
+  </si>
+  <si>
+    <t>MOTOR 4 POLOS 127V POLIA Ø20mm P/ LAV. ALTA CAPACIDADE COM PÉ</t>
   </si>
   <si>
     <t>ROTOR AGL DESL P24 4 POLOS EIXO C/ VENTOINHA</t>
@@ -250,7 +253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" width="7.33203125" min="1" max="1"/>
@@ -601,7 +604,7 @@
         <v>3</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0</v>
@@ -697,7 +700,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0</v>
@@ -1305,7 +1308,7 @@
         <v>3</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0</v>
@@ -1482,7 +1485,7 @@
     </row>
     <row r="39" customHeight="1" ht="15" spans="1:10">
       <c r="A39" s="1" t="n">
-        <v>412021</v>
+        <v>412183</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>41</v>
@@ -1497,7 +1500,7 @@
         <v>3</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>857</v>
+        <v>2478</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0</v>
@@ -1514,7 +1517,7 @@
     </row>
     <row r="40" customHeight="1" ht="15" spans="1:10">
       <c r="A40" s="1" t="n">
-        <v>412147</v>
+        <v>412021</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>42</v>
@@ -1529,7 +1532,7 @@
         <v>3</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>2813</v>
+        <v>857</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0</v>
@@ -1546,7 +1549,7 @@
     </row>
     <row r="41" customHeight="1" ht="15" spans="1:10">
       <c r="A41" s="1" t="n">
-        <v>412162</v>
+        <v>412147</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>43</v>
@@ -1561,7 +1564,7 @@
         <v>3</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>511</v>
+        <v>2813</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>0</v>
@@ -1578,7 +1581,7 @@
     </row>
     <row r="42" customHeight="1" ht="15" spans="1:10">
       <c r="A42" s="1" t="n">
-        <v>412163</v>
+        <v>412162</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>44</v>
@@ -1593,7 +1596,7 @@
         <v>3</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>466</v>
+        <v>511</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>0</v>
@@ -1610,7 +1613,7 @@
     </row>
     <row r="43" customHeight="1" ht="15" spans="1:10">
       <c r="A43" s="1" t="n">
-        <v>412393</v>
+        <v>412163</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>45</v>
@@ -1625,18 +1628,50 @@
         <v>3</v>
       </c>
       <c r="F43" s="3" t="n">
+        <v>466</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" ht="15" spans="1:10">
+      <c r="A44" s="1" t="n">
+        <v>412393</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="n">
         <v>619</v>
       </c>
-      <c r="G43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="n">
+      <c r="G44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/temp/diversos/Bobinagem.xlsx
+++ b/temp/diversos/Bobinagem.xlsx
@@ -1500,7 +1500,7 @@
         <v>3</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2478</v>
+        <v>1638</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0</v>
